--- a/data/generated/plots/ClassifiersAccuracyReal.xlsx
+++ b/data/generated/plots/ClassifiersAccuracyReal.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,13 +576,13 @@
         <v>293</v>
       </c>
       <c r="H4" t="n">
-        <v>0.918</v>
+        <v>0.915</v>
       </c>
       <c r="I4" t="n">
         <v>0.778</v>
       </c>
       <c r="J4" t="n">
-        <v>0.993</v>
+        <v>0.994</v>
       </c>
       <c r="K4" t="n">
         <v>0.973</v>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.99</v>
+        <v>0.991</v>
       </c>
       <c r="D5" t="n">
         <v>0.919</v>
@@ -615,16 +615,16 @@
       <c r="G5" t="n">
         <v>292</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I5" s="4" t="n">
+      <c r="H5" s="4" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.838</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="4" t="n">
+      <c r="J5" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.979</v>
       </c>
       <c r="L5" t="n">
@@ -655,13 +655,13 @@
       <c r="G6" s="4" t="n">
         <v>298</v>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>0.984</v>
+      <c r="H6" t="n">
+        <v>0.981</v>
       </c>
       <c r="I6" t="n">
         <v>0.837</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.899</v>
+        <v>0.902</v>
       </c>
       <c r="D7" t="n">
         <v>0.87</v>
       </c>
       <c r="E7" t="n">
-        <v>0.993</v>
+        <v>0.994</v>
       </c>
       <c r="F7" t="n">
         <v>0.987</v>
@@ -702,13 +702,53 @@
         <v>0.775</v>
       </c>
       <c r="J7" t="n">
-        <v>0.972</v>
+        <v>0.974</v>
       </c>
       <c r="K7" t="n">
         <v>0.973</v>
       </c>
       <c r="L7" s="4" t="n">
         <v>297</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VGG13</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="G8" t="n">
+        <v>297</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="L8" t="n">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
